--- a/Plan/Table/TestData/06.PackData.xlsx
+++ b/Plan/Table/TestData/06.PackData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEF21FC7-21C4-4EEA-828C-A8A67D370B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64450892-FD18-49C6-8F36-994082477847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12915" yWindow="2835" windowWidth="14505" windowHeight="13485" xr2:uid="{88C21A2F-EC59-43C7-ACF6-44ECCB6A0CA1}"/>
+    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{15E53A96-84AA-4DA5-BC0D-D5BFAF32CD07}"/>
   </bookViews>
   <sheets>
     <sheet name="06.PackData" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Pack_Id</t>
   </si>
@@ -44,16 +47,34 @@
     <t>Name_ID</t>
   </si>
   <si>
-    <t>ad01</t>
-  </si>
-  <si>
-    <t>ad01_name</t>
+    <t>tra00</t>
+  </si>
+  <si>
+    <t>tra00_name</t>
+  </si>
+  <si>
+    <t>tra01</t>
+  </si>
+  <si>
+    <t>tra01_name</t>
+  </si>
+  <si>
+    <t>tra02</t>
+  </si>
+  <si>
+    <t>tra02_name</t>
   </si>
   <si>
     <t>Gatch_Key</t>
   </si>
   <si>
     <t>Pack_Resource</t>
+  </si>
+  <si>
+    <t>Store_ToolPack_Reg.png</t>
+  </si>
+  <si>
+    <t>Store_ToolPack_Bronze.png</t>
   </si>
 </sst>
 </file>
@@ -436,9 +457,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC10F3D-C6D2-4D25-8710-44E5B9DFC280}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3EDE9C-7F5C-41F7-B1B0-22F77162B665}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -449,10 +470,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -463,10 +484,38 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Plan/Table/TestData/06.PackData.xlsx
+++ b/Plan/Table/TestData/06.PackData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64450892-FD18-49C6-8F36-994082477847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A24072D9-87A5-488F-9E63-92D4C4F4219B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{15E53A96-84AA-4DA5-BC0D-D5BFAF32CD07}"/>
+    <workbookView xWindow="12360" yWindow="3945" windowWidth="14505" windowHeight="13485" xr2:uid="{D42E4BE8-D5EA-4A01-AD82-BB7FF5EBE695}"/>
   </bookViews>
   <sheets>
     <sheet name="06.PackData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Pack_Id</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>Gatch_Key</t>
+  </si>
+  <si>
+    <t>Card_Show_Count</t>
+  </si>
+  <si>
+    <t>Card_Pick_Count</t>
   </si>
   <si>
     <t>Pack_Resource</t>
@@ -457,12 +463,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3EDE9C-7F5C-41F7-B1B0-22F77162B665}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052143B1-6B39-4329-B049-545A2C81ADC5}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -475,8 +481,14 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -487,10 +499,16 @@
         <v>100</v>
       </c>
       <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -500,11 +518,17 @@
       <c r="C3">
         <v>101</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -514,8 +538,14 @@
       <c r="C4">
         <v>102</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
